--- a/docs/en/03-domain/service-desk/ticket/reference/ticket-action-workflow-matrix.xlsx
+++ b/docs/en/03-domain/service-desk/ticket/reference/ticket-action-workflow-matrix.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="355">
   <si>
     <t>Service Desk Ticket Action Workflow Matrix</t>
   </si>
@@ -1070,6 +1070,60 @@
   </si>
   <si>
     <t>The row records a current implementation gap or policy boundary that must not be treated as completed authorization behavior.</t>
+  </si>
+  <si>
+    <t>NON_REQUESTER_OPERATIONAL_PARTICIPANT</t>
+  </si>
+  <si>
+    <t>TICKET_ACCESS_AND_NOTE_POLICY</t>
+  </si>
+  <si>
+    <t>NON_REQUESTER_OPERATIONAL_PARTICIPANT</t>
+  </si>
+  <si>
+    <t>Requires ticket visibility and current/past assignment or current category approval/assignment participation. Non-Admin requesters are excluded. Action reads and linked History use the same NOTE policy.</t>
+  </si>
+  <si>
+    <t>EFFECTIVE_USER_ADMIN</t>
+  </si>
+  <si>
+    <t>TICKET_ACCESS_AND_NOTE_POLICY</t>
+  </si>
+  <si>
+    <t>EFFECTIVE_USER_ADMIN</t>
+  </si>
+  <si>
+    <t>Effective-user Admin may access NOTE, including as requester, only after ticket visibility. Impersonation does not add the original Admin role. No note update route exists.</t>
+  </si>
+  <si>
+    <t>TICKET_ACCESS_AND_NOTE_POLICY</t>
+  </si>
+  <si>
+    <t>ORIGINAL_AUTHOR_WITH_NOTE_ACCESS</t>
+  </si>
+  <si>
+    <t>Requires original authorship and current NOTE access. Stored History remains immutable; NOTE-related reads remain filtered, including after soft delete.</t>
+  </si>
+  <si>
+    <t>LATEST_RESOLUTION_HISTORY_AT_LEAST_168_HOURS_OLD</t>
+  </si>
+  <si>
+    <t>Latest resolution History starts the 168-hour grace period, including after re-resolution. The selected REMOTE schedule checks hourly; hosted deployment and scheduled lifecycle execution remain unverified. Closure may be delayed.</t>
+  </si>
+  <si>
+    <t>TICKET_ACCESS means existing ticket visibility. NOTE additionally requires effective-user Admin or non-requester operational participation; the same policy filters NOTE Actions and linked History.</t>
+  </si>
+  <si>
+    <t>Existing COMMENT remains readable after closure. Existing NOTE remains readable only under the NOTE access policy. Closed blocks new communication and soft delete.</t>
+  </si>
+  <si>
+    <t>Resolved tickets become eligible 168 elapsed hours after the latest resolution History. The selected hourly REMOTE check is not an exact closure deadline; hosted scheduled execution remains unverified.</t>
+  </si>
+  <si>
+    <t>Latest resolution History starts the 168-hour grace period, including after re-resolution. REMOTE auto-close is verified and scheduled hourly through Supabase Cron (0 * * * *). The normal wait until the next check is less than approximately one hour; missed runs or locked Tickets can be caught up on a later run.</t>
+  </si>
+  <si>
+    <t>Resolved tickets become eligible 168 elapsed hours after the latest resolution History. REMOTE function execution and hourly Supabase Cron invocation (0 * * * *) are verified. The hourly check is not an exact closure deadline; missed runs or locked Tickets can be caught up on a later run.</t>
   </si>
 </sst>
 </file>
@@ -2132,13 +2186,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>51</v>
+        <v>337</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>27</v>
+        <v>338</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>52</v>
@@ -2171,7 +2225,7 @@
         <v>58</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="21" customFormat="1" ht="57" customHeight="1">
@@ -2182,13 +2236,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>60</v>
+        <v>341</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>27</v>
+        <v>342</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>60</v>
+        <v>343</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>52</v>
@@ -2221,7 +2275,7 @@
         <v>58</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="21" customFormat="1" ht="57" customHeight="1">
@@ -2235,10 +2289,10 @@
         <v>63</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>27</v>
+        <v>345</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>64</v>
@@ -2271,7 +2325,7 @@
         <v>58</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>76</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="21" customFormat="1" ht="57" customHeight="1">
@@ -3147,7 +3201,7 @@
         <v>124</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>167</v>
+        <v>348</v>
       </c>
       <c r="I28" s="23" t="s">
         <v>110</v>
@@ -3171,7 +3225,7 @@
         <v>170</v>
       </c>
       <c r="P28" s="24" t="s">
-        <v>171</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3315,7 @@
         <v>179</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>36</v>
@@ -3289,7 +3343,7 @@
         <v>185</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>351</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>36</v>
@@ -3331,7 +3385,7 @@
         <v>193</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>36</v>
